--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/transitory_input.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/transitory_input.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRANSIENT" sheetId="1" r:id="R5354cc5ccd6d44f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHECKPOINTS" sheetId="2" r:id="R9d119cebe0764231"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRANSIENT" sheetId="1" r:id="Rcdf0c24ed6374a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHECKPOINTS" sheetId="2" r:id="R5e04031f359748ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -452,7 +452,7 @@
   <x:sheetData>
     <x:row r="1" ht="14.5" hidden="0" customHeight="1">
       <x:c r="A1" s="28" t="str">
-        <x:v>%QUESTO E' IL MASTER DEI FILE DI INPUT</x:v>
+        <x:v>% OPENSC2 MASTER INPUT FILE</x:v>
       </x:c>
       <x:c r="B1" s="29"/>
       <x:c r="C1" s="29"/>
@@ -572,7 +572,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D8" s="36" t="str">
-        <x:v>User defined time step for the thermal-hydraulic loop. Should be in the range [STPMIN, STPMAX] (boundary included). </x:v>
+        <x:v>User-defined time step for the thermal-hydraulic loop. Must be in the range [STPMIN, STPMAX], including the bounds.</x:v>
       </x:c>
       <x:c r="E8" s="35" t="n">
         <x:v>1</x:v>
@@ -606,7 +606,7 @@
         <x:v>float</x:v>
       </x:c>
       <x:c r="D10" s="36" t="str">
-        <x:v>Maximum time step for the thermal-hydraulic loop. It is the Upper bound of the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2</x:v>
+        <x:v>Maximum time step for the thermal-hydraulic loop. It is the upper bound of the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2.</x:v>
       </x:c>
       <x:c r="E10" s="35" t="n">
         <x:v>1</x:v>
@@ -623,7 +623,7 @@
         <x:v>float or str</x:v>
       </x:c>
       <x:c r="D11" s="36" t="str">
-        <x:v>Multiplier used to tune (increase) the adaptive time step, used if flag IADAPTIME = 1 or IADAPTIME = 2; default to 1.2. Any positive real number or none. If none default value is used. </x:v>
+        <x:v>Multiplier used to increase the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2. Defaults to 1.2. Enter any positive real number or None; if None, the default value is used.</x:v>
       </x:c>
       <x:c r="E11" s="35" t="str">
         <x:v>none</x:v>
@@ -640,7 +640,7 @@
         <x:v>float or str</x:v>
       </x:c>
       <x:c r="D12" s="37" t="str">
-        <x:v>Multiplier used to tune (decrease) the adaptive time step, used if flag IADAPTIME = 1 or IADAPTIME = 2; default to 0.5. Any positive real number or none. If none default value is used. </x:v>
+        <x:v>Multiplier used to decrease the adaptive time step if IADAPTIME = 1 or IADAPTIME = 2. Defaults to 0.5. Enter any positive real number or None; if None, the default value is used.</x:v>
       </x:c>
       <x:c r="E12" s="35" t="str">
         <x:v>none</x:v>
